--- a/Interim Analyses/state_by_state_data.xlsx
+++ b/Interim Analyses/state_by_state_data.xlsx
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>5853.051892460799</v>
+        <v>5843.777495851101</v>
       </c>
     </row>
     <row r="27">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>5312.730586704597</v>
+        <v>5299.76276366598</v>
       </c>
     </row>
     <row r="28">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>5752.671852988964</v>
+        <v>5772.629882279936</v>
       </c>
     </row>
     <row r="29">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>5262.840500310187</v>
+        <v>5238.244448083297</v>
       </c>
     </row>
     <row r="30">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D30">
-        <v>5792.246438429396</v>
+        <v>5869.547913063971</v>
       </c>
     </row>
     <row r="31">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="D31">
-        <v>5554.950608208079</v>
+        <v>5568.427274354373</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D32">
-        <v>5831.074410691648</v>
+        <v>5826.104213768611</v>
       </c>
     </row>
     <row r="33">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D33">
-        <v>5287.549305809509</v>
+        <v>5281.229327936688</v>
       </c>
     </row>
     <row r="34">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="D34">
-        <v>5731.143066350396</v>
+        <v>5756.012062712214</v>
       </c>
     </row>
     <row r="35">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D35">
-        <v>5232.875707752293</v>
+        <v>5217.562651871074</v>
       </c>
     </row>
     <row r="36">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="D36">
-        <v>5774.228286341281</v>
+        <v>5855.475115768649</v>
       </c>
     </row>
     <row r="37">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D37">
-        <v>5517.15240246851</v>
+        <v>5535.745751534127</v>
       </c>
     </row>
     <row r="38">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="D44">
-        <v>5744.126110274991</v>
+        <v>5763.96471136649</v>
       </c>
     </row>
     <row r="45">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="D45">
-        <v>5256.057623660815</v>
+        <v>5281.576366692782</v>
       </c>
     </row>
     <row r="46">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D46">
-        <v>5548.115762293479</v>
+        <v>5576.760534160294</v>
       </c>
     </row>
     <row r="47">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="D47">
-        <v>4988.218479526076</v>
+        <v>4909.947065024034</v>
       </c>
     </row>
     <row r="48">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D48">
-        <v>5625.650778347259</v>
+        <v>5685.098395947156</v>
       </c>
     </row>
     <row r="49">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="D49">
-        <v>5550.471872806261</v>
+        <v>5616.947184028864</v>
       </c>
     </row>
     <row r="50">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="D50">
-        <v>5700.494681809336</v>
+        <v>5707.498747636712</v>
       </c>
     </row>
     <row r="51">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="D51">
-        <v>5183.538620755409</v>
+        <v>5199.572967842032</v>
       </c>
     </row>
     <row r="52">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="D52">
-        <v>5509.575085255551</v>
+        <v>5539.010522584713</v>
       </c>
     </row>
     <row r="53">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="D53">
-        <v>4949.086104508867</v>
+        <v>4882.910340374691</v>
       </c>
     </row>
     <row r="54">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D54">
-        <v>5592.971262889583</v>
+        <v>5653.186311217607</v>
       </c>
     </row>
     <row r="55">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="D55">
-        <v>5451.196971715241</v>
+        <v>5497.845922054836</v>
       </c>
     </row>
     <row r="56">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D62">
-        <v>5667.635267981549</v>
+        <v>5641.568180154768</v>
       </c>
     </row>
     <row r="63">
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="D63">
-        <v>5158.097581735437</v>
+        <v>5201.823932149533</v>
       </c>
     </row>
     <row r="64">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D64">
-        <v>5417.829901674246</v>
+        <v>5415.941765750629</v>
       </c>
     </row>
     <row r="65">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="D65">
-        <v>4902.91942085522</v>
+        <v>4841.659006732367</v>
       </c>
     </row>
     <row r="66">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="D66">
-        <v>5382.888900720067</v>
+        <v>5424.194220562767</v>
       </c>
     </row>
     <row r="67">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="D67">
-        <v>5495.389343578405</v>
+        <v>5594.019914706362</v>
       </c>
     </row>
     <row r="68">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="D68">
-        <v>5526.870446475684</v>
+        <v>5449.298878662536</v>
       </c>
     </row>
     <row r="69">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D69">
-        <v>4966.376336198342</v>
+        <v>4949.488278156392</v>
       </c>
     </row>
     <row r="70">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D70">
-        <v>5343.829615078643</v>
+        <v>5327.735841763868</v>
       </c>
     </row>
     <row r="71">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="D71">
-        <v>4842.686418292964</v>
+        <v>4790.612189485048</v>
       </c>
     </row>
     <row r="72">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D72">
-        <v>5318.741559434503</v>
+        <v>5347.303730973446</v>
       </c>
     </row>
     <row r="73">
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="D73">
-        <v>5371.014338218048</v>
+        <v>5443.003808867108</v>
       </c>
     </row>
     <row r="74">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D80">
-        <v>5311.011834805262</v>
+        <v>5090.573194166461</v>
       </c>
     </row>
     <row r="81">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="D81">
-        <v>4702.144998827666</v>
+        <v>4594.61026383373</v>
       </c>
     </row>
     <row r="82">
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="D82">
-        <v>5127.188164406522</v>
+        <v>5054.297313257021</v>
       </c>
     </row>
     <row r="83">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="D83">
-        <v>4740.832835420022</v>
+        <v>4665.921941246549</v>
       </c>
     </row>
     <row r="84">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="D84">
-        <v>5133.951503320106</v>
+        <v>5097.564991961642</v>
       </c>
     </row>
     <row r="85">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="D85">
-        <v>5459.138505668908</v>
+        <v>5614.747791535856</v>
       </c>
     </row>
     <row r="86">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D86">
-        <v>5270.666054674259</v>
+        <v>5073.965777049915</v>
       </c>
     </row>
     <row r="87">
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="D87">
-        <v>4687.881776141716</v>
+        <v>4605.586678750062</v>
       </c>
     </row>
     <row r="88">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="D88">
-        <v>5099.9609548549</v>
+        <v>5039.928643272306</v>
       </c>
     </row>
     <row r="89">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="D89">
-        <v>4667.243354922846</v>
+        <v>4598.50161116524</v>
       </c>
     </row>
     <row r="90">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D90">
-        <v>5113.036326545673</v>
+        <v>5090.351800761662</v>
       </c>
     </row>
     <row r="91">
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="D91">
-        <v>5313.530607977463</v>
+        <v>5434.019245752053</v>
       </c>
     </row>
     <row r="92">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="D98">
-        <v>5028.458128817642</v>
+        <v>4748.587236682551</v>
       </c>
     </row>
     <row r="99">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="D99">
-        <v>4408.450152332111</v>
+        <v>4227.446779244891</v>
       </c>
     </row>
     <row r="100">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="D100">
-        <v>4888.443395998298</v>
+        <v>4770.634111032953</v>
       </c>
     </row>
     <row r="101">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="D101">
-        <v>4661.325785062453</v>
+        <v>4509.425877744216</v>
       </c>
     </row>
     <row r="102">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="D102">
-        <v>4959.967777664897</v>
+        <v>4891.694353460814</v>
       </c>
     </row>
     <row r="103">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="D103">
-        <v>5337.166328565325</v>
+        <v>5481.422548883797</v>
       </c>
     </row>
     <row r="104">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="D104">
-        <v>5037.374127197179</v>
+        <v>4766.96736632421</v>
       </c>
     </row>
     <row r="105">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="D105">
-        <v>4406.844266230294</v>
+        <v>4259.070542723267</v>
       </c>
     </row>
     <row r="106">
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="D106">
-        <v>4858.856520233947</v>
+        <v>4754.64076030688</v>
       </c>
     </row>
     <row r="107">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="D107">
-        <v>4591.799634514242</v>
+        <v>4450.37997268423</v>
       </c>
     </row>
     <row r="108">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="D108">
-        <v>4946.659240330448</v>
+        <v>4885.785528051604</v>
       </c>
     </row>
     <row r="109">
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="D109">
-        <v>5329.630641836122</v>
+        <v>5516.908719482642</v>
       </c>
     </row>
     <row r="110">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="D116">
-        <v>4963.102227347845</v>
+        <v>4604.447038994565</v>
       </c>
     </row>
     <row r="117">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="D117">
-        <v>4428.826517911273</v>
+        <v>4172.640180210918</v>
       </c>
     </row>
     <row r="118">
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="D118">
-        <v>4837.044522514876</v>
+        <v>4648.020759574749</v>
       </c>
     </row>
     <row r="119">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="D119">
-        <v>4600.501347521449</v>
+        <v>4341.458314624811</v>
       </c>
     </row>
     <row r="120">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D120">
-        <v>4671.989686265486</v>
+        <v>4583.619901736047</v>
       </c>
     </row>
     <row r="121">
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="D121">
-        <v>5262.661143108731</v>
+        <v>5245.6002978744</v>
       </c>
     </row>
     <row r="122">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="D122">
-        <v>4708.787116977061</v>
+        <v>4474.49209467831</v>
       </c>
     </row>
     <row r="123">
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="D123">
-        <v>4368.843860469387</v>
+        <v>4238.925455025241</v>
       </c>
     </row>
     <row r="124">
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="D124">
-        <v>4692.653865210924</v>
+        <v>4568.047959841465</v>
       </c>
     </row>
     <row r="125">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="D125">
-        <v>4351.152275242513</v>
+        <v>4171.452229691165</v>
       </c>
     </row>
     <row r="126">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="D126">
-        <v>4536.523006967855</v>
+        <v>4504.785699958518</v>
       </c>
     </row>
     <row r="127">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="D127">
-        <v>5342.755848357265</v>
+        <v>5594.687754935907</v>
       </c>
     </row>
     <row r="128">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="D134">
-        <v>4826.965194899152</v>
+        <v>4456.190835514011</v>
       </c>
     </row>
     <row r="135">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="D135">
-        <v>4504.169630958357</v>
+        <v>4204.817510913555</v>
       </c>
     </row>
     <row r="136">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="D136">
-        <v>4718.332222053945</v>
+        <v>4513.628096165632</v>
       </c>
     </row>
     <row r="137">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D137">
-        <v>4452.376501353338</v>
+        <v>4162.627396731004</v>
       </c>
     </row>
     <row r="138">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="D138">
-        <v>4518.750624804448</v>
+        <v>4415.887317886503</v>
       </c>
     </row>
     <row r="139">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="D139">
-        <v>5086.945223675584</v>
+        <v>5002.585246588973</v>
       </c>
     </row>
     <row r="140">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="D140">
-        <v>4959.568605380926</v>
+        <v>4920.018648271136</v>
       </c>
     </row>
     <row r="141">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="D141">
-        <v>4878.272162956006</v>
+        <v>4926.054974778623</v>
       </c>
     </row>
     <row r="142">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="D142">
-        <v>4901.287579254</v>
+        <v>4964.686676792207</v>
       </c>
     </row>
     <row r="143">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="D143">
-        <v>4238.369091249378</v>
+        <v>4071.042045386099</v>
       </c>
     </row>
     <row r="144">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="D144">
-        <v>4674.340158947707</v>
+        <v>4817.03076506346</v>
       </c>
     </row>
     <row r="145">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="D145">
-        <v>5372.263047143629</v>
+        <v>5708.728623695059</v>
       </c>
     </row>
     <row r="146">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="D152">
-        <v>4709.447107604672</v>
+        <v>4344.943729732529</v>
       </c>
     </row>
     <row r="153">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="D153">
-        <v>4432.252617049711</v>
+        <v>4145.556614672521</v>
       </c>
     </row>
     <row r="154">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D154">
-        <v>4622.70864087955</v>
+        <v>4408.611034678554</v>
       </c>
     </row>
     <row r="155">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="D155">
-        <v>4316.13104346491</v>
+        <v>4005.809120130184</v>
       </c>
     </row>
     <row r="156">
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="D156">
-        <v>4403.04361046797</v>
+        <v>4287.658647009517</v>
       </c>
     </row>
     <row r="157">
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="D157">
-        <v>5138.193689049294</v>
+        <v>5105.080601895132</v>
       </c>
     </row>
     <row r="158">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="D158">
-        <v>4920.684894811706</v>
+        <v>4934.410680639921</v>
       </c>
     </row>
     <row r="159">
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="D159">
-        <v>5014.896878009966</v>
+        <v>5187.767818062741</v>
       </c>
     </row>
     <row r="160">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="D160">
-        <v>4842.959873087437</v>
+        <v>4934.040520071303</v>
       </c>
     </row>
     <row r="161">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="D161">
-        <v>4283.788326360204</v>
+        <v>4181.805511103294</v>
       </c>
     </row>
     <row r="162">
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="D162">
-        <v>4591.831809033067</v>
+        <v>4753.764192888152</v>
       </c>
     </row>
     <row r="163">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="D163">
-        <v>5166.811860245649</v>
+        <v>5442.494271884088</v>
       </c>
     </row>
     <row r="164">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="D170">
-        <v>4705.897934960351</v>
+        <v>4368.11876245746</v>
       </c>
     </row>
     <row r="171">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="D171">
-        <v>4408.562724162026</v>
+        <v>4137.076648288993</v>
       </c>
     </row>
     <row r="172">
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="D172">
-        <v>4600.293583733855</v>
+        <v>4420.635351194801</v>
       </c>
     </row>
     <row r="173">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="D173">
-        <v>4226.392478251953</v>
+        <v>3914.951057200903</v>
       </c>
     </row>
     <row r="174">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="D174">
-        <v>4346.995802182488</v>
+        <v>4264.230882715291</v>
       </c>
     </row>
     <row r="175">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="D175">
-        <v>5016.596753239518</v>
+        <v>4947.316297934129</v>
       </c>
     </row>
     <row r="176">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="D176">
-        <v>4800.469339422034</v>
+        <v>4786.019114520455</v>
       </c>
     </row>
     <row r="177">
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="D177">
-        <v>4679.619373570862</v>
+        <v>4744.817800141134</v>
       </c>
     </row>
     <row r="178">
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="D178">
-        <v>4703.521411905333</v>
+        <v>4781.119582287853</v>
       </c>
     </row>
     <row r="179">
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="D179">
-        <v>4398.452072214406</v>
+        <v>4388.356604211933</v>
       </c>
     </row>
     <row r="180">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="D180">
-        <v>4429.401742091111</v>
+        <v>4585.86220704382</v>
       </c>
     </row>
     <row r="181">
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="D181">
-        <v>5098.062360369262</v>
+        <v>5391.46310398487</v>
       </c>
     </row>
     <row r="182">
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="D187">
-        <v>4628.857672493992</v>
+        <v>4309.713825848525</v>
       </c>
     </row>
     <row r="188">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="D188">
-        <v>4383.635097136772</v>
+        <v>4149.114484614793</v>
       </c>
     </row>
     <row r="189">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="D189">
-        <v>4547.673919475007</v>
+        <v>4381.939549785487</v>
       </c>
     </row>
     <row r="190">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="D190">
-        <v>4266.718396145909</v>
+        <v>3940.325921698709</v>
       </c>
     </row>
     <row r="191">
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="D191">
-        <v>4276.149267723834</v>
+        <v>4202.988635210646</v>
       </c>
     </row>
     <row r="192">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="D192">
-        <v>4731.402373150465</v>
+        <v>4734.254754710953</v>
       </c>
     </row>
     <row r="193">
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="D193">
-        <v>4534.897992192389</v>
+        <v>4594.676023673525</v>
       </c>
     </row>
     <row r="194">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="D194">
-        <v>4693.443013423995</v>
+        <v>4820.805901301969</v>
       </c>
     </row>
     <row r="195">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="D195">
-        <v>4427.718939831157</v>
+        <v>4409.838346132266</v>
       </c>
     </row>
     <row r="196">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="D196">
-        <v>4402.621422973411</v>
+        <v>4607.649816565461</v>
       </c>
     </row>
     <row r="197">
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="D202">
-        <v>4596.564503413329</v>
+        <v>4294.628231937629</v>
       </c>
     </row>
     <row r="203">
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="D203">
-        <v>4363.029133740274</v>
+        <v>4157.093124861138</v>
       </c>
     </row>
     <row r="204">
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="D204">
-        <v>4488.176202990587</v>
+        <v>4338.912745022335</v>
       </c>
     </row>
     <row r="205">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="D205">
-        <v>4237.930665530765</v>
+        <v>3934.274534443884</v>
       </c>
     </row>
     <row r="206">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="D206">
-        <v>4186.720209453431</v>
+        <v>4128.287871705048</v>
       </c>
     </row>
     <row r="207">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="D207">
-        <v>4580.443098803379</v>
+        <v>4553.614065032738</v>
       </c>
     </row>
     <row r="208">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="D208">
-        <v>4373.707788081645</v>
+        <v>4423.098534327823</v>
       </c>
     </row>
     <row r="209">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D209">
-        <v>4533.867151531347</v>
+        <v>4640.341373948786</v>
       </c>
     </row>
     <row r="210">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="D210">
-        <v>4340.395861650052</v>
+        <v>4338.600488354403</v>
       </c>
     </row>
     <row r="211">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="D211">
-        <v>4219.96092826957</v>
+        <v>4405.827397407595</v>
       </c>
     </row>
     <row r="212">
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="D217">
-        <v>4398.149431946665</v>
+        <v>4058.565750785378</v>
       </c>
     </row>
     <row r="218">
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="D218">
-        <v>4180.555951563314</v>
+        <v>3937.823683456895</v>
       </c>
     </row>
     <row r="219">
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="D219">
-        <v>4323.415727299256</v>
+        <v>4135.694500383293</v>
       </c>
     </row>
     <row r="220">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="D220">
-        <v>4154.802494645076</v>
+        <v>3859.689791617216</v>
       </c>
     </row>
     <row r="221">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="D221">
-        <v>3999.188017130749</v>
+        <v>3905.42250103495</v>
       </c>
     </row>
     <row r="222">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="D222">
-        <v>4322.392056768914</v>
+        <v>4265.705479525862</v>
       </c>
     </row>
     <row r="223">
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="D223">
-        <v>4195.629429653663</v>
+        <v>4222.080790995708</v>
       </c>
     </row>
     <row r="224">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="D224">
-        <v>4346.726584524215</v>
+        <v>4418.91356383884</v>
       </c>
     </row>
     <row r="225">
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="D225">
-        <v>4230.280547128175</v>
+        <v>4242.775663001725</v>
       </c>
     </row>
     <row r="226">
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="D226">
-        <v>4009.336305065818</v>
+        <v>4163.850681688074</v>
       </c>
     </row>
     <row r="227">
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="D232">
-        <v>4239.61902815447</v>
+        <v>3881.327968263782</v>
       </c>
     </row>
     <row r="233">
@@ -4549,7 +4549,7 @@
         </is>
       </c>
       <c r="D233">
-        <v>4051.954218739287</v>
+        <v>3779.204520380764</v>
       </c>
     </row>
     <row r="234">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="D234">
-        <v>4181.004995447167</v>
+        <v>3971.219596246618</v>
       </c>
     </row>
     <row r="235">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="D235">
-        <v>4025.553984887099</v>
+        <v>3725.491172042142</v>
       </c>
     </row>
     <row r="236">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="D236">
-        <v>3833.406238684349</v>
+        <v>3717.781131629958</v>
       </c>
     </row>
     <row r="237">
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="D237">
-        <v>4294.711422781525</v>
+        <v>4279.788409952976</v>
       </c>
     </row>
     <row r="238">
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="D238">
-        <v>4173.483062208557</v>
+        <v>4252.34629387211</v>
       </c>
     </row>
     <row r="239">
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="D239">
-        <v>4310.859044064112</v>
+        <v>4431.956760283554</v>
       </c>
     </row>
     <row r="240">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="D240">
-        <v>4058.087095162387</v>
+        <v>4062.287422352805</v>
       </c>
     </row>
     <row r="241">
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="D241">
-        <v>3944.880442711691</v>
+        <v>4143.975509958769</v>
       </c>
     </row>
     <row r="242">
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="D247">
-        <v>4079.556610492908</v>
+        <v>3704.947150877026</v>
       </c>
     </row>
     <row r="248">
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="D248">
-        <v>3914.206666209074</v>
+        <v>3621.990611319026</v>
       </c>
     </row>
     <row r="249">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="D249">
-        <v>4063.3733931737</v>
+        <v>3841.182712729249</v>
       </c>
     </row>
     <row r="250">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="D250">
-        <v>3874.647263364679</v>
+        <v>3544.43766214083</v>
       </c>
     </row>
     <row r="251">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="D251">
-        <v>3693.188205041512</v>
+        <v>3565.614183477612</v>
       </c>
     </row>
     <row r="252">
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="D252">
-        <v>4048.15257567233</v>
+        <v>3994.795602158863</v>
       </c>
     </row>
     <row r="253">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="D253">
-        <v>3944.696900461578</v>
+        <v>3979.149553397137</v>
       </c>
     </row>
     <row r="254">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="D254">
-        <v>4101.188149441368</v>
+        <v>4175.557424154544</v>
       </c>
     </row>
     <row r="255">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="D255">
-        <v>3925.691666712767</v>
+        <v>3922.44105597944</v>
       </c>
     </row>
     <row r="256">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="D256">
-        <v>3718.998190467749</v>
+        <v>3873.013304971313</v>
       </c>
     </row>
     <row r="257">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="D262">
-        <v>3943.219880429167</v>
+        <v>3554.627218755651</v>
       </c>
     </row>
     <row r="263">
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="D263">
-        <v>3822.360362911353</v>
+        <v>3516.725999749989</v>
       </c>
     </row>
     <row r="264">
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="D264">
-        <v>3950.681868360069</v>
+        <v>3711.31254591509</v>
       </c>
     </row>
     <row r="265">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="D265">
-        <v>3758.75282570507</v>
+        <v>3408.686386678299</v>
       </c>
     </row>
     <row r="266">
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="D266">
-        <v>3564.107283028053</v>
+        <v>3423.115801372104</v>
       </c>
     </row>
     <row r="267">
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="D267">
-        <v>3923.028832186607</v>
+        <v>3875.274537615239</v>
       </c>
     </row>
     <row r="268">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="D268">
-        <v>3835.646043576301</v>
+        <v>3876.919703571751</v>
       </c>
     </row>
     <row r="269">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="D269">
-        <v>3990.471988885773</v>
+        <v>4064.435103976441</v>
       </c>
     </row>
     <row r="270">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D270">
-        <v>3831.858421110728</v>
+        <v>3832.634133639422</v>
       </c>
     </row>
     <row r="271">
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="D271">
-        <v>3588.886233088129</v>
+        <v>3742.136098987584</v>
       </c>
     </row>
     <row r="272">
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="D277">
-        <v>3835.604740689456</v>
+        <v>3444.08945436206</v>
       </c>
     </row>
     <row r="278">
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="D278">
-        <v>3733.383280970788</v>
+        <v>3421.561046790902</v>
       </c>
     </row>
     <row r="279">
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="D279">
-        <v>3863.08367421622</v>
+        <v>3620.475477194997</v>
       </c>
     </row>
     <row r="280">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="D280">
-        <v>3640.720025605134</v>
+        <v>3282.092923612885</v>
       </c>
     </row>
     <row r="281">
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="D281">
-        <v>3456.089565744699</v>
+        <v>3313.233054496225</v>
       </c>
     </row>
     <row r="282">
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="D282">
-        <v>3811.126944855226</v>
+        <v>3770.257860899114</v>
       </c>
     </row>
     <row r="283">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="D283">
-        <v>3722.853006767573</v>
+        <v>3766.377206529872</v>
       </c>
     </row>
     <row r="284">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="D284">
-        <v>3866.493210128059</v>
+        <v>3932.669076885215</v>
       </c>
     </row>
     <row r="285">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="D285">
-        <v>3644.778192504373</v>
+        <v>3624.899029890516</v>
       </c>
     </row>
     <row r="286">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="D286">
-        <v>3442.766650794134</v>
+        <v>3587.604597813951</v>
       </c>
     </row>
     <row r="287">
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="D292">
-        <v>3715.18313378685</v>
+        <v>3313.17887267811</v>
       </c>
     </row>
     <row r="293">
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="D293">
-        <v>3621.337844691059</v>
+        <v>3293.891096182169</v>
       </c>
     </row>
     <row r="294">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="D294">
-        <v>3777.694484981119</v>
+        <v>3522.783879636956</v>
       </c>
     </row>
     <row r="295">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="D295">
-        <v>3555.208639759765</v>
+        <v>3183.206754252869</v>
       </c>
     </row>
     <row r="296">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="D296">
-        <v>3337.824748255861</v>
+        <v>3186.28299480658</v>
       </c>
     </row>
     <row r="297">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="D297">
-        <v>3687.808849959634</v>
+        <v>3650.570322219815</v>
       </c>
     </row>
     <row r="298">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="D298">
-        <v>3599.103252836366</v>
+        <v>3633.350050490124</v>
       </c>
     </row>
     <row r="299">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="D299">
-        <v>3825.06177544882</v>
+        <v>3916.802273291322</v>
       </c>
     </row>
     <row r="300">
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="D300">
-        <v>3545.696875492262</v>
+        <v>3520.827638657194</v>
       </c>
     </row>
     <row r="301">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="D301">
-        <v>3365.060756366872</v>
+        <v>3537.709539848352</v>
       </c>
     </row>
     <row r="302">
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="D307">
-        <v>3605.083626571338</v>
+        <v>3193.415813042589</v>
       </c>
     </row>
     <row r="308">
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="D308">
-        <v>3526.293675726686</v>
+        <v>3185.134670161842</v>
       </c>
     </row>
     <row r="309">
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="D309">
-        <v>3687.902225643441</v>
+        <v>3423.648097668161</v>
       </c>
     </row>
     <row r="310">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="D310">
-        <v>3460.668484020709</v>
+        <v>3083.466490852702</v>
       </c>
     </row>
     <row r="311">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="D311">
-        <v>3227.677216168092</v>
+        <v>3067.18836026518</v>
       </c>
     </row>
     <row r="312">
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="D312">
-        <v>3614.121609074403</v>
+        <v>3601.519185665066</v>
       </c>
     </row>
     <row r="313">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="D313">
-        <v>3545.535364032768</v>
+        <v>3604.910360098007</v>
       </c>
     </row>
     <row r="314">
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="D314">
-        <v>3771.046321513832</v>
+        <v>3888.807317368988</v>
       </c>
     </row>
     <row r="315">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="D315">
-        <v>3448.141466895818</v>
+        <v>3431.518710922676</v>
       </c>
     </row>
     <row r="316">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="D316">
-        <v>3284.032810334889</v>
+        <v>3479.404534364538</v>
       </c>
     </row>
     <row r="317">
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="D322">
-        <v>3528.773524013915</v>
+        <v>3118.57379604558</v>
       </c>
     </row>
     <row r="323">
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="D323">
-        <v>3459.069744036987</v>
+        <v>3117.12052928424</v>
       </c>
     </row>
     <row r="324">
@@ -6187,7 +6187,7 @@
         </is>
       </c>
       <c r="D324">
-        <v>3620.66188280482</v>
+        <v>3358.44539020489</v>
       </c>
     </row>
     <row r="325">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="D325">
-        <v>3379.234078150364</v>
+        <v>2994.634264349203</v>
       </c>
     </row>
     <row r="326">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="D326">
-        <v>3143.294236302265</v>
+        <v>2986.815143155179</v>
       </c>
     </row>
     <row r="327">
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="D327">
-        <v>3589.071341617524</v>
+        <v>3616.942857032257</v>
       </c>
     </row>
     <row r="328">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="D328">
-        <v>3556.442442795646</v>
+        <v>3652.577539763738</v>
       </c>
     </row>
     <row r="329">
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="D329">
-        <v>3753.912165104962</v>
+        <v>3916.968825615607</v>
       </c>
     </row>
     <row r="330">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="D330">
-        <v>3415.46291389727</v>
+        <v>3424.068518533985</v>
       </c>
     </row>
     <row r="331">
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="D331">
-        <v>3252.958533249489</v>
+        <v>3497.60952285341</v>
       </c>
     </row>
     <row r="332">
@@ -6421,7 +6421,7 @@
         </is>
       </c>
       <c r="D337">
-        <v>3470.391242264593</v>
+        <v>3067.301169158559</v>
       </c>
     </row>
     <row r="338">
@@ -6439,7 +6439,7 @@
         </is>
       </c>
       <c r="D338">
-        <v>3409.961140642181</v>
+        <v>3074.842037715005</v>
       </c>
     </row>
     <row r="339">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="D339">
-        <v>3582.379728490401</v>
+        <v>3330.926154165688</v>
       </c>
     </row>
     <row r="340">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="D340">
-        <v>3318.635340557894</v>
+        <v>2930.815497169902</v>
       </c>
     </row>
     <row r="341">
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="D341">
-        <v>3079.360621417673</v>
+        <v>2933.870604683748</v>
       </c>
     </row>
     <row r="342">
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="D342">
-        <v>3590.272987469216</v>
+        <v>3656.778003003808</v>
       </c>
     </row>
     <row r="343">
@@ -6529,7 +6529,7 @@
         </is>
       </c>
       <c r="D343">
-        <v>3557.308486331627</v>
+        <v>3691.088564953925</v>
       </c>
     </row>
     <row r="344">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="D344">
-        <v>3758.355983827252</v>
+        <v>3973.056010685703</v>
       </c>
     </row>
     <row r="345">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="D345">
-        <v>3405.718169444479</v>
+        <v>3445.768304079749</v>
       </c>
     </row>
     <row r="346">
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="D346">
-        <v>3226.476918224448</v>
+        <v>3520.303922246617</v>
       </c>
     </row>
     <row r="347">
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="D352">
-        <v>3371.327288093957</v>
+        <v>2959.865677264986</v>
       </c>
     </row>
     <row r="353">
@@ -6709,7 +6709,7 @@
         </is>
       </c>
       <c r="D353">
-        <v>3329.912065032566</v>
+        <v>2983.994929917189</v>
       </c>
     </row>
     <row r="354">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="D354">
-        <v>3509.49527138228</v>
+        <v>3248.996787791039</v>
       </c>
     </row>
     <row r="355">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="D355">
-        <v>3269.266919357492</v>
+        <v>2881.750268026529</v>
       </c>
     </row>
     <row r="356">
@@ -6763,7 +6763,7 @@
         </is>
       </c>
       <c r="D356">
-        <v>2987.913378343796</v>
+        <v>2834.964013846457</v>
       </c>
     </row>
     <row r="357">
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="D357">
-        <v>3476.201958489058</v>
+        <v>3540.130347927166</v>
       </c>
     </row>
     <row r="358">
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="D358">
-        <v>3443.468011667988</v>
+        <v>3569.361644974811</v>
       </c>
     </row>
     <row r="359">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="D359">
-        <v>3678.887003362353</v>
+        <v>3889.908111768966</v>
       </c>
     </row>
     <row r="360">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="D360">
-        <v>3400.891665368332</v>
+        <v>3475.24576113941</v>
       </c>
     </row>
     <row r="361">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="D361">
-        <v>3119.335784947813</v>
+        <v>3416.393919928754</v>
       </c>
     </row>
     <row r="362">
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="D367">
-        <v>3258.935357924628</v>
+        <v>2830.741599595169</v>
       </c>
     </row>
     <row r="368">
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="D368">
-        <v>3239.243185369763</v>
+        <v>2878.970245314169</v>
       </c>
     </row>
     <row r="369">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="D369">
-        <v>3393.235173023742</v>
+        <v>3102.445615731044</v>
       </c>
     </row>
     <row r="370">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="D370">
-        <v>3179.879109285783</v>
+        <v>2784.672604997165</v>
       </c>
     </row>
     <row r="371">
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="D371">
-        <v>2864.218938440939</v>
+        <v>2684.271526390436</v>
       </c>
     </row>
     <row r="372">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="D372">
-        <v>3301.740422261355</v>
+        <v>3337.135717021438</v>
       </c>
     </row>
     <row r="373">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="D373">
-        <v>3304.03234852452</v>
+        <v>3408.749458908041</v>
       </c>
     </row>
     <row r="374">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="D374">
-        <v>3513.692619686117</v>
+        <v>3685.136356412436</v>
       </c>
     </row>
     <row r="375">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="D375">
-        <v>3316.911523276248</v>
+        <v>3400.520579171604</v>
       </c>
     </row>
     <row r="376">
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="D376">
-        <v>2947.990890812231</v>
+        <v>3209.320157462311</v>
       </c>
     </row>
     <row r="377">
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="D382">
-        <v>3177.865202136588</v>
+        <v>2745.845689981325</v>
       </c>
     </row>
     <row r="383">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="D383">
-        <v>3174.412985493539</v>
+        <v>2803.69821075723</v>
       </c>
     </row>
     <row r="384">
@@ -7267,7 +7267,7 @@
         </is>
       </c>
       <c r="D384">
-        <v>3336.021799092509</v>
+        <v>3037.050102289363</v>
       </c>
     </row>
     <row r="385">
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="D385">
-        <v>3073.412387789491</v>
+        <v>2666.779934738864</v>
       </c>
     </row>
     <row r="386">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="D386">
-        <v>2788.772600504744</v>
+        <v>2603.540939564353</v>
       </c>
     </row>
     <row r="387">
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="D387">
-        <v>3177.399496931491</v>
+        <v>3205.304012808358</v>
       </c>
     </row>
     <row r="388">
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="D388">
-        <v>3189.702451710307</v>
+        <v>3278.94474065179</v>
       </c>
     </row>
     <row r="389">
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="D389">
-        <v>3423.379448283406</v>
+        <v>3589.39165623079</v>
       </c>
     </row>
     <row r="390">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="D390">
-        <v>3170.250421870164</v>
+        <v>3243.50371111934</v>
       </c>
     </row>
     <row r="391">
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="D391">
-        <v>2846.144724649705</v>
+        <v>3107.178310809898</v>
       </c>
     </row>
     <row r="392">
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="D397">
-        <v>3110.01041950806</v>
+        <v>2678.035499431506</v>
       </c>
     </row>
     <row r="398">
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="D398">
-        <v>3118.604580223168</v>
+        <v>2746.250657652693</v>
       </c>
     </row>
     <row r="399">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="D399">
-        <v>3297.058571700642</v>
+        <v>2997.086364149015</v>
       </c>
     </row>
     <row r="400">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="D400">
-        <v>2989.981149615173</v>
+        <v>2567.5832412224</v>
       </c>
     </row>
     <row r="401">
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="D401">
-        <v>2732.352774876488</v>
+        <v>2548.418033690077</v>
       </c>
     </row>
     <row r="402">
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c r="D402">
-        <v>3133.235032923424</v>
+        <v>3177.302707831112</v>
       </c>
     </row>
     <row r="403">
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="D403">
-        <v>3141.980947328591</v>
+        <v>3243.386054641381</v>
       </c>
     </row>
     <row r="404">
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="D404">
-        <v>3397.707643854462</v>
+        <v>3591.324791177458</v>
       </c>
     </row>
     <row r="405">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="D405">
-        <v>3049.559929913284</v>
+        <v>3108.20860961117</v>
       </c>
     </row>
     <row r="406">
@@ -7663,7 +7663,7 @@
         </is>
       </c>
       <c r="D406">
-        <v>2808.352831213054</v>
+        <v>3101.8371606586</v>
       </c>
     </row>
     <row r="407">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="D412">
-        <v>3078.297828872403</v>
+        <v>2640.665284219839</v>
       </c>
     </row>
     <row r="413">
@@ -7789,7 +7789,7 @@
         </is>
       </c>
       <c r="D413">
-        <v>3099.40446865628</v>
+        <v>2723.126296850734</v>
       </c>
     </row>
     <row r="414">
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="D414">
-        <v>3273.584734800109</v>
+        <v>2970.327313128636</v>
       </c>
     </row>
     <row r="415">
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="D415">
-        <v>2955.490351944699</v>
+        <v>2532.523631505946</v>
       </c>
     </row>
     <row r="416">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="D416">
-        <v>2716.548653055763</v>
+        <v>2531.02806689689</v>
       </c>
     </row>
     <row r="417">
@@ -7861,7 +7861,7 @@
         </is>
       </c>
       <c r="D417">
-        <v>3073.888036103002</v>
+        <v>3121.881637246969</v>
       </c>
     </row>
     <row r="418">
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="D418">
-        <v>3080.462943209816</v>
+        <v>3182.526883798859</v>
       </c>
     </row>
     <row r="419">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="D419">
-        <v>3344.231569057983</v>
+        <v>3545.116717798423</v>
       </c>
     </row>
     <row r="420">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="D420">
-        <v>3000.635135043291</v>
+        <v>3075.686981712374</v>
       </c>
     </row>
     <row r="421">
@@ -7933,7 +7933,7 @@
         </is>
       </c>
       <c r="D421">
-        <v>2767.234211350074</v>
+        <v>3070.034945957491</v>
       </c>
     </row>
   </sheetData>
